--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1574,12 +1574,12 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mI5QoG4QmG4QmG4Q</t>
+          <t>Ngk6PZj3Ndj3NZj3</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:36</t>
+          <t>HDU checksum updated 2026-01-07T18:03:57</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:36</t>
+          <t>data unit checksum updated 2026-01-07T18:03:57</t>
         </is>
       </c>
     </row>
@@ -1672,16 +1672,52 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEQSTART</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
           <t>NIRDALevel1HDUList</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1930,12 +1966,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>k4eBn4e9k4eAk4e7</t>
+          <t>k5eAk3d8k3dAk3d7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:36</t>
+          <t>HDU checksum updated 2026-01-07T18:03:58</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1989,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:36</t>
+          <t>data unit checksum updated 2026-01-07T18:03:58</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2388,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zp3Iho3FZo3Ffo3F</t>
+          <t>Zq3Ggn2FZn2Fdn2F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:36</t>
+          <t>HDU checksum updated 2026-01-07T18:03:58</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2411,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:36</t>
+          <t>data unit checksum updated 2026-01-07T18:03:58</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +782,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v2.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -818,7 +818,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INTEGRTS</t>
+          <t>GRPS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1309,14 +1309,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SC_Integrations value for acquire</t>
+          <t>SC_Groups value for acquire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EXPOSRES</t>
+          <t>INTEGRTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1327,32 +1327,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SC_Exposures value for acquire</t>
+          <t>SC_Integrations value for acquire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENDDELAY</t>
+          <t>EXPOSRES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SC_EndDelay value for acquire</t>
+          <t>SC_Exposures value for acquire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RSTSINC</t>
+          <t>ENDDELAY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1363,14 +1363,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reset frames included in datacube?</t>
+          <t>SC_EndDelay value for acquire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DRPSINC</t>
+          <t>RSTSINC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1381,50 +1381,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Drop frames included in datacube?</t>
+          <t>Reset frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FRMSTOT</t>
+          <t>DRPSINC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Total #frames clocked in acquire</t>
+          <t>Drop frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FRMSEXP</t>
+          <t>FRMSTOT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>#frames expected to be acquired from MACIE/SIDE</t>
+          <t>Total #frames clocked in acquire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRMSACQ</t>
+          <t>FRMSEXP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1435,208 +1435,208 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#frames actually acquired from  MACIE/SIDECAR</t>
+          <t>#frames expected to be acquired from MACIE/SIDE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRPSAVGD</t>
+          <t>FRMSACQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Whether groups were averaged (1) or not (0)</t>
+          <t>#frames actually acquired from  MACIE/SIDECAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAMPGAIN</t>
+          <t>GRPSAVGD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pre-amp gain based on gain register value.</t>
+          <t>Whether groups were averaged (1) or not (0)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FRMTIME</t>
+          <t>PAMPGAIN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Frame time in ms</t>
+          <t>Pre-amp gain based on gain register value.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TSIDECAR</t>
+          <t>FRMTIME</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SIDECAR Temperature at start of integration</t>
+          <t>Frame time in ms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TCOMPRJT</t>
+          <t>TSIDECAR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CCE Compressor Reject Temperature at start of i</t>
+          <t>SIDECAR Temperature at start of integration</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TCLDTIP1</t>
+          <t>TCOMPRJT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>297.6682434082031</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CCE Cold Tip1 Temperature at start of integrati</t>
+          <t>CCE Compressor Reject Temperature at start of i</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TCLDTIP2</t>
+          <t>TCLDTIP1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>78.88285064697266</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CCE Cold Tip2 Temperature at start of integrati</t>
+          <t>CCE Cold Tip1 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>TCLDTIP2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ngk6PZj3Ndj3NZj3</t>
+          <t>68.87708282470703</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:57</t>
+          <t>CCE Cold Tip2 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>CacgDZZfCaafCYYf</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:57</t>
+          <t>HDU checksum updated 2026-01-08T14:08:02</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0.4.2</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:08:02</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TARG_RA</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Target right ascension [deg]</t>
-        </is>
-      </c>
+          <t>0.4.2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TARG_DEC</t>
+          <t>TARG_RA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1647,77 +1647,113 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Target declination [deg]</t>
+          <t>Target right ascension [deg]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>TARG_DEC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Commanded roll [deg]</t>
+          <t>Target declination [deg]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>TARG_RLL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>Commanded roll [deg]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Observation Sequence Start</t>
+          <t>DPC Observation ID</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>SEQSTART</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
+          <t>2454833</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>NIRDALevel1HDUList</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-01-08T19:08:02.744</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1966,12 +2002,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>k5eAk3d8k3dAk3d7</t>
+          <t>j8dEm5d9j5dCj5d9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:58</t>
+          <t>HDU checksum updated 2026-01-08T14:08:03</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2025,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:58</t>
+          <t>data unit checksum updated 2026-01-08T14:08:03</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2424,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zq3Ggn2FZn2Fdn2F</t>
+          <t>Z12Jg12HZ12Hd12H</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:58</t>
+          <t>HDU checksum updated 2026-01-08T14:08:03</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2447,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:58</t>
+          <t>data unit checksum updated 2026-01-08T14:08:03</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -1592,12 +1592,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CacgDZZfCaafCYYf</t>
+          <t>OeHZRZ9ZOdGZOZ9Z</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:02</t>
+          <t>HDU checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:02</t>
+          <t>data unit checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-08T19:08:02.744</t>
+          <t>2026-01-16T17:20:01.999</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2002,12 +2002,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>j8dEm5d9j5dCj5d9</t>
+          <t>m7hEn6f9m6fEm6f9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:03</t>
+          <t>HDU checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:03</t>
+          <t>data unit checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Z12Jg12HZ12Hd12H</t>
+          <t>b36Ic14Ib14Ib14I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:03</t>
+          <t>HDU checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:03</t>
+          <t>data unit checksum updated 2026-01-16T10:20:02</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -10,7 +10,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,21 +474,6 @@
         </is>
       </c>
       <c r="C3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BinTableHDU</t>
-        </is>
-      </c>
-      <c r="C4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1592,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OeHZRZ9ZOdGZOZ9Z</t>
+          <t>RdHXTZ9WRbGWRZ9W</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:02</t>
+          <t>HDU checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:02</t>
+          <t>data unit checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1730,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-16T17:20:01.999</t>
+          <t>2026-01-16T22:40:15.212</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2002,12 +1986,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>m7hEn6f9m6fEm6f9</t>
+          <t>m6gAm3f9m3fAm3f7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:02</t>
+          <t>HDU checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2009,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:02</t>
+          <t>data unit checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>
@@ -2056,400 +2040,6 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BINTABLE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BINTABLE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>binary table extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of dimension 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>number of group parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TFIELDS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>b36Ic14Ib14Ib14I</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:02</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -10,6 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Primary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext3" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +478,66 @@
         </is>
       </c>
       <c r="C3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BinTableHDU</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BinTableHDU</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -488,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +830,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v2.08</t>
+          <t>v3.03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,7 +866,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -820,7 +884,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>WASP-178b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -838,7 +902,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/04/05/2025-04-05__13-15-18_InfImg_d2048x2048x0050_b1_e01_i01_g01_d00_r50.sp</t>
+          <t>/sssp/data/2026/05/08/2026-05-08__01-26-18_InfImg_WASP-178b_d0080x0400x1488_b1_e01_i62_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,7 +974,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -928,7 +992,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>907</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -964,7 +1028,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -982,7 +1046,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1000,7 +1064,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>372</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1036,7 +1100,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1054,7 +1118,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>797174156</t>
+          <t>831518815</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1136,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>738000000</t>
+          <t>835000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,7 +1244,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1216,7 +1280,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1234,7 +1298,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1270,7 +1334,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1288,7 +1352,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1306,7 +1370,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1396,7 +1460,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1414,7 +1478,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1432,7 +1496,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1450,7 +1514,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1468,7 +1532,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.65685</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1486,7 +1550,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1504,7 +1568,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>-3.4849305152893066</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1586,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>261.29901123046875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1604,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>136.4371337890625</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1622,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>126.43830871582031</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1640,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RdHXTZ9WRbGWRZ9W</t>
+          <t>VJB6W9A6VGA6V9A6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:15</t>
+          <t>HDU checksum updated 2026-06-10T14:51:10</t>
         </is>
       </c>
     </row>
@@ -1599,20 +1663,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:15</t>
+          <t>data unit checksum updated 2026-06-10T14:51:10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>FOWLER</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0.4.2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1626,7 +1690,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227.27029418945312</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1644,7 +1708,7 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-42.70498275756836</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1656,67 +1720,67 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TARG_RLL</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>227.26834778055903</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Commanded roll [deg]</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DPCSEQID</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>-42.70592109518633</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DPC Obseravation Sequence ID</t>
+          <t>Executed DEC [deg]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEQSTART</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2454833</t>
+          <t>27.678795411293407</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DPC Observation Sequence Start</t>
+          <t>Executed roll [deg]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NIRDALevel1HDUList</t>
+          <t>0.4.8</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -1724,20 +1788,296 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-01-16T22:40:15.212</t>
+          <t>Gaia DR3 6003809889735481856</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>Gaia DR3 source ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GAIARA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>227.27032703913977</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Gaia DR3 RA in J2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GAIADEC</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>-42.70496654225058</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Gaia DR3 DEC in J2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PARALLAX</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2.424837486926974</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Gaia DR3 parallax</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PMRA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>-10.24347465311499</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmra</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PMDEC</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-5.63608880634272</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Gaia DR3 pmdec</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2MASSID</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2MASS J15090488-4242178</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2MASS source ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>J_M</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>9.775</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2MASS j magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>H_M</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9.735</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2MASS h magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>K_M</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9.703</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>G_M</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>9.915789179327074</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Gaia DR3 g magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BP_M</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>9.950138912095703</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>RP_M</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>9.833647482812413</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>NIRDALevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-06-10T18:51:10.945</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>Pandora DPC Processing Time</t>
         </is>
       </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Appended Vectors.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1750,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1805,17 +2145,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -1837,7 +2177,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -1850,10 +2190,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1864,10 +2208,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1878,10 +2226,14 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1937,109 +2289,2439 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>name of this binary table extension</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>WCSAXES</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32768</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Number of coordinate axes</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BSCALE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>CRPIX1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>1781.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pixel coordinate of reference point</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>m6gAm3f9m3fAm3f7</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:15</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1494830781</t>
+          <t>-0.46451433866911</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:15</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>0.88556559845716</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.4.2</t>
+          <t>-0.88556559845716</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PC2_2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-0.46451433866911</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Coordinate transformation matrix element</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CDELT1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CDELT2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.00033055555555556</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate increment at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CUNIT1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CUNIT2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Units of coordinate increment and value</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CTYPE1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>RA---TAN</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Right ascension, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CTYPE2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DEC--TAN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Declination, gnomonic projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CRVAL1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>227.26834778056</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CRVAL2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-42.705921095186</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[deg] Coordinate value at reference point</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LONPOLE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[deg] Native longitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LATPOLE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-42.705921095186</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[deg] Native latitude of celestial pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MJDREF</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[d] MJD of fiducial time</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RADESYS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COUNTS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PFSOFTV</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.4.8</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bIOabHMTbHMYbHMY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>182456715</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:11</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11996</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DWPDDUODDUODDUOD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2773363002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>integration_time</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>integration_time</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TTYPE18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TFORM18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ZJT4a9S3VGS3Z9S3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3988589176</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BSCALE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>O3afO3RcO3XcO3Xc</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>571941338</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONTAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7.71192801620913e-07</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Flux not from the target in aperture in e/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COMPLTE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.9999181864563139</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fraction of flux from the target in aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TOTAP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>49064.37291628969</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Total flux expected in aperture in e/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>227.2702866086426</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-42.7049828893777</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1086.4985658919675</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1775.4844227214326</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6003809889735481856</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0OVp3LUm0LUm0LUm</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>202771108</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -14,6 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,12 +487,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C4" t="b">
@@ -499,12 +502,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VECTORS</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -514,12 +517,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>INTEGRATION</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -529,16 +532,293 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BinTableHDU</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WAVELENGTH</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HV6BHU6BHU6BHU6B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1665654538</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -552,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -830,7 +1110,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.03</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -884,7 +1164,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WASP-178b</t>
+          <t>WASP-18b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -902,7 +1182,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/05/08/2026-05-08__01-26-18_InfImg_WASP-178b_d0080x0400x1488_b1_e01_i62_g06_d16_r04.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__15-36-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -992,7 +1272,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>962</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1046,7 +1326,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1064,7 +1344,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>546</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1118,7 +1398,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>831518815</t>
+          <t>836149015</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1136,7 +1416,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>835000000</t>
+          <t>860000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1244,7 +1524,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>261</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1370,7 +1650,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1460,7 +1740,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1478,7 +1758,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1496,7 +1776,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1550,7 +1830,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1568,7 +1848,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-3.4849305152893066</t>
+          <t>-8.405950546264648</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1586,7 +1866,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>261.29901123046875</t>
+          <t>277.5338134765625</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1604,7 +1884,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>136.4371337890625</t>
+          <t>131.91334533691406</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1622,7 +1902,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>126.43830871582031</t>
+          <t>120.00798797607422</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1640,12 +1920,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VJB6W9A6VGA6V9A6</t>
+          <t>SDEMT9ELSCELS9EL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:10</t>
+          <t>HDU checksum updated 2026-07-15T15:20:54</t>
         </is>
       </c>
     </row>
@@ -1663,20 +1943,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:10</t>
+          <t>data unit checksum updated 2026-07-15T15:20:54</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOWLER</t>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1684,400 +1964,500 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TARG_RA</t>
+          <t>COLLAPS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>227.27029418945312</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Target right ascension [deg]</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TARG_DEC</t>
+          <t>TARG_RA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-42.70498275756836</t>
+          <t>24.354568481445312</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Target declination [deg]</t>
+          <t>Target right ascension [deg]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>TARG_DEC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>227.26834778055903</t>
+          <t>-45.677734375</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Executed RA [deg]</t>
+          <t>Target declination [deg]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEC</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-42.70592109518633</t>
+          <t>24.354116273831984</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Executed DEC [deg]</t>
+          <t>Executed RA [deg]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ROLL</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>27.678795411293407</t>
+          <t>-45.67608017214077</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Executed roll [deg]</t>
+          <t>Executed DEC [deg]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>ROLL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0.4.8</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>140.7491762998052</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Executed roll [deg]</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GAIADR3</t>
+          <t>POS_X</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gaia DR3 6003809889735481856</t>
+          <t>1775.5199731765706</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Gaia DR3 source ID</t>
+          <t>X [column] Pixel position of target</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GAIARA</t>
+          <t>POS_Y</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>227.27032703913977</t>
+          <t>1086.4261338175227</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Gaia DR3 RA in J2016</t>
+          <t>Y [row] Pixel position of target</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GAIADEC</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-42.70496654225058</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Gaia DR3 DEC in J2016</t>
-        </is>
-      </c>
+          <t>0.5.0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PARALLAX</t>
+          <t>PRSOFTV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2.424837486926974</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Gaia DR3 parallax</t>
-        </is>
-      </c>
+          <t>2.6.0</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PMRA</t>
+          <t>GAIADR3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>-10.24347465311499</t>
+          <t>Gaia DR3 4955371367334610048</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmra</t>
+          <t>Gaia DR3 source ID</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PMDEC</t>
+          <t>GAIARA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-5.63608880634272</t>
+          <t>24.3544669330396</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Gaia DR3 pmdec</t>
+          <t>Gaia DR3 RA in J2016</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2MASSID</t>
+          <t>GAIADEC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2MASS J15090488-4242178</t>
+          <t>-45.6777908467995</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2MASS source ID</t>
+          <t>Gaia DR3 DEC in J2016</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>J_M</t>
+          <t>PARALLAX</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>9.775</t>
+          <t>8.144292282321743</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2MASS j magnitude</t>
+          <t>Gaia DR3 parallax</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>H_M</t>
+          <t>PMRA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9.735</t>
+          <t>25.404449269627033</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2MASS h magnitude</t>
+          <t>Gaia DR3 pmra</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>K_M</t>
+          <t>PMDEC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>9.703</t>
+          <t>20.47932580565009</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2MASS k magnitude</t>
+          <t>Gaia DR3 pmdec</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>G_M</t>
+          <t>2MASSID</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9.915789179327074</t>
+          <t>2MASS J01372503-4540404</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Gaia DR3 g magnitude</t>
+          <t>2MASS source ID</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BP_M</t>
+          <t>J_M</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>9.950138912095703</t>
+          <t>8.409</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Gaia DR3 bp magnitude</t>
+          <t>2MASS j magnitude</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RP_M</t>
+          <t>H_M</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9.833647482812413</t>
+          <t>8.231</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Gaia DR3 rp magnitude</t>
+          <t>2MASS h magnitude</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>K_M</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NIRDALevel1HDUList</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>8.131</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2MASS k magnitude</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PFTIME</t>
+          <t>G_M</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-06-10T18:51:10.945</t>
+          <t>9.173880843192613</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Pandora DPC Processing Time</t>
+          <t>Gaia DR3 g magnitude</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>BP_M</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Appended WCS.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>9.411079659286305</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Gaia DR3 bp magnitude</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>RP_M</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
+          <t>8.777077857991749</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gaia DR3 rp magnitude</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TEFF</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>6311.6724</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Gaia DR3 Teff</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>LOGG</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4.2654</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Gaia DR3 logg</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PFCLASS</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NIRDALevel1HDUList</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PFTIME</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-15T19:20:54.311</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Appended WCS.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
           <t>Appended Vectors.</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2090,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,7 +2588,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2226,7 +2606,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2296,49 +2676,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Number of coordinate axes</t>
-        </is>
-      </c>
+          <t>ct / s</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1781.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1085.0</t>
+          <t>1781.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2350,31 +2726,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.46451433866911</t>
+          <t>1085.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.88556559845716</t>
+          <t>-0.63271646138296</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2386,13 +2762,13 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.88556559845716</t>
+          <t>-0.77438354805292</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2404,13 +2780,13 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.46451433866911</t>
+          <t>0.77438354805292</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2422,25 +2798,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.00033055555555556</t>
+          <t>-0.63271646138296</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -2458,25 +2834,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>0.00033055555555556</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -2494,67 +2870,67 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RA---TAN</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Right ascension, gnomonic projection</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEC--TAN</t>
+          <t>RA---TAN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Declination, gnomonic projection</t>
+          <t>Right ascension, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>227.26834778056</t>
+          <t>DEC--TAN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>Declination, gnomonic projection</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-42.705921095186</t>
+          <t>24.354116273832</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2566,136 +2942,126 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>-45.676080172141</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-42.705921095186</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-45.676080172141</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>COUNTS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>ICRS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Equatorial coordinate system</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PFSOFTV</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.4.8</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>FA2YF31YFA1YF31Y</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:56</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bIOabHMTbHMYbHMY</t>
+          <t>1613408595</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>182456715</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:11</t>
+          <t>data unit checksum updated 2026-07-15T15:20:56</t>
         </is>
       </c>
     </row>
@@ -2710,7 +3076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2743,17 +3109,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -2765,12 +3131,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2787,12 +3153,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2810,322 +3176,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>FRAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Time frame is JD</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JD</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>38Wa45UT35UY35UY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PCOTemp</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PCOTemp</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DWPDDUODDUODDUOD</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2773363002</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>1128785080</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3173,17 +3337,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3359,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3217,12 +3381,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3240,790 +3404,120 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of dimension 1</t>
-        </is>
-      </c>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>second</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>Exposure time unit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>EXPTIME</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avg_ra</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>avg_ra</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>T5AfW53cT59cT59c</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avg_dec</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>avg_dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avg_rot</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>avg_rot</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>err_ra</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>err_ra</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>err_dec</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>err_dec</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>err_rot</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>err_rot</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>jd</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>jd</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>integration_time</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>integration_time</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>sep</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>sep</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>missing</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>earth_angle</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>earth_angle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>earth_illumination</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>earth_illumination</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sun_angle</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>sun_angle</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TTYPE15</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>visda_keepout</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>visda_keepout</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>TFORM15</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>TTYPE16</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>nirda_keepout</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>nirda_keepout</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TFORM16</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TTYPE17</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>posx</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>posx</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>TFORM17</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TTYPE18</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>posy</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>posy</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TFORM18</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>VECTORS</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>VECTORS</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ZJT4a9S3VGS3Z9S3</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>3988589176</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>2149502507</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
         </is>
       </c>
     </row>
@@ -4038,7 +3532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4093,17 +3587,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4115,17 +3609,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4138,160 +3632,102 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAXIS2</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INTEGRATION</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>INTEGRATION</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>hXa5jWT3hWZ3hWZ3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>O3afO3RcO3XcO3Xc</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>571941338</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>20475</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
         </is>
       </c>
     </row>
@@ -4306,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4339,17 +3775,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -4361,17 +3797,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4393,7 +3829,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4406,12 +3842,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -4424,12 +3860,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -4447,7 +3883,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -4472,254 +3908,1422 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.71192801620913e-07</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Flux not from the target in aperture in e/s</t>
-        </is>
-      </c>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.9999181864563139</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fraction of flux from the target in aperture</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PCOTemp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>eADmg09le7Ale79l</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>563707308</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BINTABLE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>binary table extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TTYPE1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avg_ra</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>avg_dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>avg_rot</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>err_ra</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>err_dec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>err_rot</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>exptime</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>target_sep</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>vitl_frames_count</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>vitl_missing_frames</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>earth_angle</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>earth_illumination</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sun_angle</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTYPE15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>visda_keepout</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TFORM15</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTYPE16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nirda_keepout</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TFORM16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TTYPE17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>posx</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TFORM17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TTYPE18</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>posy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TFORM18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VECTORS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>id89kb89ib89ib89</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2743892109</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BSCALE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BZERO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>32768</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>49064.37291628969</t>
+          <t>A4aiC3YhA3ahA3Wh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total flux expected in aperture in e/s</t>
+          <t>HDU checksum updated 2026-07-15T15:20:59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>227.2702866086426</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-42.7049828893777</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1086.4985658919675</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1775.4844227214326</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GAIA_ID</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>6003809889735481856</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0OVp3LUm0LUm0LUm</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-06-10T14:51:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>202771108</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-06-10T14:51:12</t>
+          <t>335287306</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-07-15T15:20:59</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -794,12 +794,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HV6BHU6BHU6BHU6B</t>
+          <t>7OAXBM2X9M9XAM9X</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1665654538</t>
+          <t>2503905330</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__15-36-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__07-32-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1398,7 +1398,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>836149015</t>
+          <t>836119976</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1416,7 +1416,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>860000000</t>
+          <t>284000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1848,7 +1848,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-8.405950546264648</t>
+          <t>-8.596685409545898</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1866,7 +1866,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>277.5338134765625</t>
+          <t>278.990966796875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1884,7 +1884,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.91334533691406</t>
+          <t>131.82008361816406</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1902,7 +1902,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.00798797607422</t>
+          <t>120.00270080566406</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1920,12 +1920,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SDEMT9ELSCELS9EL</t>
+          <t>9aS4IVS39ZS3GZS3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:54</t>
+          <t>HDU checksum updated 2026-07-23T15:43:45</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:54</t>
+          <t>data unit checksum updated 2026-07-23T15:43:45</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>24.354568481445312</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2002,7 +2002,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>-45.677734375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2020,7 +2020,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>24.354116273831984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2038,7 +2038,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-45.67608017214077</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2056,7 +2056,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>140.7491762998052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2074,7 +2074,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1775.5199731765706</t>
+          <t>1780.0000000000107</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2092,7 +2092,7 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1086.4261338175227</t>
+          <t>1084.0</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2138,7 +2138,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gaia DR3 4955371367334610048</t>
+          <t>Gaia DR3 2738188646457069696</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2156,7 +2156,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>24.3544669330396</t>
+          <t>359.9895648280386</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2174,7 +2174,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-45.6777908467995</t>
+          <t>0.0122193084231721</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2192,7 +2192,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>8.144292282321743</t>
+          <t>1.7823902563684113</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>25.404449269627033</t>
+          <t>-1.4543602775194662</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2228,7 +2228,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>20.47932580565009</t>
+          <t>-20.56395362712824</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2246,7 +2246,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2MASS J01372503-4540404</t>
+          <t>2MASS J23595750+0000443</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2264,7 +2264,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>8.409</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2282,7 +2282,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>8.231</t>
+          <t>13.194</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>8.131</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2318,7 +2318,7 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9.173880843192613</t>
+          <t>15.30356771429766</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2336,7 +2336,7 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9.411079659286305</t>
+          <t>15.829263614564265</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2354,7 +2354,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>8.777077857991749</t>
+          <t>14.617636552444335</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2372,7 +2372,7 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>6311.6724</t>
+          <t>4694.66</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2390,7 +2390,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4.2654</t>
+          <t>4.4039</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2422,7 +2422,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-07-15T19:20:54.311</t>
+          <t>2026-07-23T19:43:45.629</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2750,7 +2750,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.63271646138296</t>
+          <t>6.1232339957368e-17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2768,7 +2768,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.77438354805292</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2786,7 +2786,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.77438354805292</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2804,7 +2804,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.63271646138296</t>
+          <t>6.1232339957368e-17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2930,7 +2930,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>24.354116273832</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2948,7 +2948,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-45.676080172141</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2984,7 +2984,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-45.676080172141</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3038,12 +3038,12 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FA2YF31YFA1YF31Y</t>
+          <t>UaYGXTYDUYYDUYYD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:56</t>
+          <t>HDU checksum updated 2026-07-23T15:43:48</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1613408595</t>
+          <t>866660619</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:56</t>
+          <t>data unit checksum updated 2026-07-23T15:43:48</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3266,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>38Wa45UT35UY35UY</t>
+          <t>OTJoQSJmOSJmOSJm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3284,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1128785080</t>
+          <t>3430194512</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T5AfW53cT59cT59c</t>
+          <t>T7AeV62eT69eT69e</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3704,12 +3704,12 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hXa5jWT3hWZ3hWZ3</t>
+          <t>hZZ7iXZ4hXZ4hXZ4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4134,12 +4134,12 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eADmg09le7Ale79l</t>
+          <t>ZW4acT2UZT2abT2U</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -4152,12 +4152,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>563707308</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>id89kb89ib89ib89</t>
+          <t>LnjaNljRLljXLljX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2743892109</t>
+          <t>2411659260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -5300,12 +5300,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A4aiC3YhA3ahA3Wh</t>
+          <t>A6akB4XiA4aiA4Wi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:59</t>
+          <t>HDU checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:59</t>
+          <t>data unit checksum updated 2026-07-23T15:43:51</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -1624,12 +1624,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GDeiI9ZZGCdfG9ZZ</t>
+          <t>GAeiG9ZZGAdfG7ZZ</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:26</t>
+          <t>HDU checksum updated 2026-09-08T14:41:26</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:26</t>
+          <t>data unit checksum updated 2026-09-08T14:41:26</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:26.116</t>
+          <t>2026-09-08T18:41:26.126</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2004,12 +2004,12 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA5hJ25fG85fG85f</t>
+          <t>HA8gJ05eH75eH75e</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:28</t>
+          <t>HDU checksum updated 2026-09-08T14:41:28</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:28</t>
+          <t>data unit checksum updated 2026-09-08T14:41:28</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>F1bmH0akF0akF0ak</t>
+          <t>GpblGobjGobjGobj</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:30</t>
+          <t>HDU checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:30</t>
+          <t>data unit checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZVa2aSU1VSa1ZSU1</t>
+          <t>UUa1aRX0WRa0aRU0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:30</t>
+          <t>HDU checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:30</t>
+          <t>data unit checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9X6KGX6J9X6JGX6J</t>
+          <t>9W9JJW6I9W6IGW6I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:30</t>
+          <t>HDU checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:30</t>
+          <t>data unit checksum updated 2026-09-08T14:41:30</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level1_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level1_nirda.xlsx
@@ -868,7 +868,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -886,7 +886,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-20_InfImg_HD_200654_d0080x0250x1583_b1_e01_i427_g02_d16_r04.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__06-44-18_InfImg_KELT-9b_d0080x0250x3096_b1_e01_i387_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>774</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1102,7 +1102,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>840078241</t>
+          <t>840091495</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>877000000</t>
+          <t>832000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1354,7 +1354,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1462,7 +1462,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1480,7 +1480,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1552,7 +1552,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.5968567132949829</t>
+          <t>3.3816466331481934</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1570,7 +1570,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>276.0766906738281</t>
+          <t>278.990966796875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1588,7 +1588,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.3281707763672</t>
+          <t>131.50372314453125</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1606,7 +1606,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.02909851074219</t>
+          <t>120.03438568115234</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1624,12 +1624,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GAeiG9ZZGAdfG7ZZ</t>
+          <t>EOXEFNVBENVBENVB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:26</t>
+          <t>HDU checksum updated 2026-09-09T15:45:55</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:26</t>
+          <t>data unit checksum updated 2026-09-09T15:45:55</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:26.126</t>
+          <t>2026-09-09T19:45:55.608</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1896,7 +1896,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1959,77 +1959,65 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>name of this binary table extension</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BZERO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>32768</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>32768</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>iX5ajU2SiU2YiU2Y</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-09-09T15:46:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UNIT</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ct</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>1317043718</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-09-09T15:46:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HA8gJ05eH75eH75e</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-09-08T14:41:28</t>
-        </is>
-      </c>
+          <t>ct</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3345064256</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-09-08T14:41:28</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2170,7 +2158,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2260,12 +2248,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GpblGobjGobjGobj</t>
+          <t>ZLiAaJi5UJiAZJi5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:30</t>
+          <t>HDU checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2266,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1569140766</t>
+          <t>4049659845</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:30</t>
+          <t>data unit checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2414,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2516,12 +2504,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UUa1aRX0WRa0aRU0</t>
+          <t>6S3a9R3U6R3Z6R3Z</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:30</t>
+          <t>HDU checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2522,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>403258811</t>
+          <t>379881537</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:30</t>
+          <t>data unit checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2670,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2754,12 +2742,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9W9JJW6I9W6IGW6I</t>
+          <t>oT5aqR3UoR3aoR3U</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:30</t>
+          <t>HDU checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2760,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>149382</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:30</t>
+          <t>data unit checksum updated 2026-09-09T15:46:04</t>
         </is>
       </c>
     </row>
